--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/dmpCfgOutput.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/dmpCfgOutput.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25230" windowHeight="11355"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="中台拉取任务表" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>系统名称</t>
   </si>
@@ -81,9 +81,6 @@
   </si>
   <si>
     <t>{.systemName}</t>
-  </si>
-  <si>
-    <t>{.code}</t>
   </si>
   <si>
     <t>{.inputConvertType}</t>
@@ -1324,69 +1321,66 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="18" width="30" customWidth="1"/>
+    <col min="1" max="17" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:20">
+    <row r="1" ht="15" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:19">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -1438,11 +1432,8 @@
       <c r="Q2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="R2" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="R2" s="2"/>
       <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
